--- a/docs/acceptance/exports/EXP-2026-0001_Elaine-Xin-Yu-Khoo.xlsx
+++ b/docs/acceptance/exports/EXP-2026-0001_Elaine-Xin-Yu-Khoo.xlsx
@@ -88,7 +88,7 @@
     <t>Approved at</t>
   </si>
   <si>
-    <t>2026-09-18T07:11:04.947Z</t>
+    <t>2026-09-19T03:10:08.358Z</t>
   </si>
   <si>
     <t>Advances</t>
@@ -193,10 +193,10 @@
     <t>MoMo Cafe Dinner Food Room# 128 : CHECK# 11603551 [pbhun211] TAN SUAN KUAN #126= +5 more</t>
   </si>
   <si>
-    <t>INR→SGD 0.01341, European Central Bank reference rate for 1 Sep 2026, via Frankfurter, fetched 18 Sep 2026 15:11 SGT.</t>
-  </si>
-  <si>
-    <t>INR→SGD 0.01341, European Central Bank reference rate for 4 Sep 2026, via Frankfurter, fetched 18 Sep 2026 15:11 SGT.</t>
+    <t>INR→SGD 0.0134111, European Central Bank reference rate for 1 Sep 2026, via Frankfurter, fetched 19 Sep 2026 11:10 SGT.</t>
+  </si>
+  <si>
+    <t>INR→SGD 0.0134073, European Central Bank reference rate for 4 Sep 2026, via Frankfurter, fetched 19 Sep 2026 11:10 SGT.</t>
   </si>
   <si>
     <t>Policy: rate on the receipt date. Each line is converted and rounded to the cent; the total is the sum of the lines.</t>
@@ -721,7 +721,7 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>1776.78</v>
+        <v>1776.61</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -729,7 +729,7 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>1776.78</v>
+        <v>1776.61</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +832,7 @@
         <v>20737.5</v>
       </c>
       <c r="J2">
-        <v>0.01341</v>
+        <v>0.01341111781667002</v>
       </c>
       <c r="K2" t="s">
         <v>41</v>
@@ -841,7 +841,7 @@
         <v>48</v>
       </c>
       <c r="M2" s="2">
-        <v>278.09</v>
+        <v>278.11</v>
       </c>
       <c r="N2" t="s">
         <v>49</v>
@@ -873,7 +873,7 @@
         <v>20738.5</v>
       </c>
       <c r="J3">
-        <v>0.01341</v>
+        <v>0.01341111781667002</v>
       </c>
       <c r="K3" t="s">
         <v>41</v>
@@ -882,7 +882,7 @@
         <v>48</v>
       </c>
       <c r="M3" s="2">
-        <v>278.1</v>
+        <v>278.13</v>
       </c>
       <c r="N3" t="s">
         <v>49</v>
@@ -914,7 +914,7 @@
         <v>1417</v>
       </c>
       <c r="J4">
-        <v>0.01341</v>
+        <v>0.01341111781667002</v>
       </c>
       <c r="K4" t="s">
         <v>41</v>
@@ -958,7 +958,7 @@
         <v>1416</v>
       </c>
       <c r="J5">
-        <v>0.01341</v>
+        <v>0.01341111781667002</v>
       </c>
       <c r="K5" t="s">
         <v>41</v>
@@ -999,7 +999,7 @@
         <v>44071.86</v>
       </c>
       <c r="J6">
-        <v>0.01341</v>
+        <v>0.013407341860402757</v>
       </c>
       <c r="K6" t="s">
         <v>17</v>
@@ -1008,7 +1008,7 @@
         <v>48</v>
       </c>
       <c r="M6" s="2">
-        <v>591</v>
+        <v>590.89</v>
       </c>
       <c r="N6" t="s">
         <v>55</v>
@@ -1043,7 +1043,7 @@
         <v>35772.84</v>
       </c>
       <c r="J7">
-        <v>0.01341</v>
+        <v>0.013407341860402757</v>
       </c>
       <c r="K7" t="s">
         <v>17</v>
@@ -1052,7 +1052,7 @@
         <v>48</v>
       </c>
       <c r="M7" s="2">
-        <v>479.71</v>
+        <v>479.62</v>
       </c>
       <c r="N7" t="s">
         <v>55</v>
@@ -1084,7 +1084,7 @@
         <v>6426.57</v>
       </c>
       <c r="J8">
-        <v>0.01341</v>
+        <v>0.013407341860402757</v>
       </c>
       <c r="K8" t="s">
         <v>17</v>
@@ -1093,7 +1093,7 @@
         <v>48</v>
       </c>
       <c r="M8" s="2">
-        <v>86.18</v>
+        <v>86.16</v>
       </c>
       <c r="N8" t="s">
         <v>55</v>
@@ -1128,7 +1128,7 @@
         <v>1917.5</v>
       </c>
       <c r="J9">
-        <v>0.01341</v>
+        <v>0.013407341860402757</v>
       </c>
       <c r="K9" t="s">
         <v>17</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="M10" s="3">
         <f>SUM(M2:M9)</f>
-        <v>1776.78</v>
+        <v>1776.61</v>
       </c>
       <c r="N10" s="1"/>
     </row>
